--- a/research/traditional_assets/database/data/argentina/argentina_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.379</v>
+        <v>0.5395000000000001</v>
       </c>
       <c r="E2">
-        <v>0.191</v>
+        <v>0.267</v>
       </c>
       <c r="F2">
-        <v>0.149</v>
+        <v>-0.161</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0004089388539845986</v>
+        <v>0.0004391868468675198</v>
       </c>
       <c r="J2">
-        <v>0.0003304636432582388</v>
+        <v>0.0003379176766895401</v>
       </c>
       <c r="K2">
-        <v>513.6899999999999</v>
+        <v>589.8</v>
       </c>
       <c r="L2">
-        <v>0.08420871446837808</v>
+        <v>0.0808742869679684</v>
       </c>
       <c r="M2">
-        <v>148.2041</v>
+        <v>160.5228</v>
       </c>
       <c r="N2">
-        <v>0.01768566450673636</v>
+        <v>0.02165539756630602</v>
       </c>
       <c r="O2">
-        <v>0.2885088282816485</v>
+        <v>0.2721648016276704</v>
       </c>
       <c r="P2">
-        <v>148.2041</v>
+        <v>157.6728</v>
       </c>
       <c r="Q2">
-        <v>0.01768566450673636</v>
+        <v>0.02127091708712192</v>
       </c>
       <c r="R2">
-        <v>0.2885088282816485</v>
+        <v>0.2673326551373347</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01775448721303142</v>
       </c>
       <c r="U2">
-        <v>7231.9</v>
+        <v>6159</v>
       </c>
       <c r="V2">
-        <v>0.8630055251255981</v>
+        <v>0.8308825513315166</v>
       </c>
       <c r="W2">
-        <v>0.04844528431540972</v>
+        <v>0.07976441557072586</v>
       </c>
       <c r="X2">
-        <v>0.1318912654108914</v>
+        <v>0.186052825288072</v>
       </c>
       <c r="Y2">
-        <v>-0.08344598109548169</v>
+        <v>-0.1062884097173461</v>
       </c>
       <c r="Z2">
-        <v>1.671269376092159</v>
+        <v>1.259760803258136</v>
       </c>
       <c r="AA2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1261382243276472</v>
+        <v>0.1752489537315164</v>
       </c>
       <c r="AC2">
-        <v>-0.1234183566309753</v>
+        <v>-0.1738360873714611</v>
       </c>
       <c r="AD2">
-        <v>3558.3</v>
+        <v>3735.4</v>
       </c>
       <c r="AE2">
-        <v>6.17695601461576</v>
+        <v>5.535490815822754</v>
       </c>
       <c r="AF2">
-        <v>3564.476956014616</v>
+        <v>3740.935490815823</v>
       </c>
       <c r="AG2">
-        <v>-3667.423043985384</v>
+        <v>-2418.064509184177</v>
       </c>
       <c r="AH2">
-        <v>0.298423012698014</v>
+        <v>0.3354035582615242</v>
       </c>
       <c r="AI2">
-        <v>0.2756562426616123</v>
+        <v>0.2712466910329091</v>
       </c>
       <c r="AJ2">
-        <v>-0.7782368122362038</v>
+        <v>-0.4841420215414672</v>
       </c>
       <c r="AK2">
-        <v>-0.6435230519952954</v>
+        <v>-0.3168059724709479</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>953.9678284182306</v>
+        <v>866.6821345707658</v>
       </c>
       <c r="AP2">
-        <v>-983.223336189111</v>
+        <v>-561.035848998649</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banco Santander Río S.A. (BASE:BRIO)</t>
+          <t>Banco Macro S.A. (BASE:BMA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.462</v>
+        <v>0.581</v>
       </c>
       <c r="E3">
-        <v>0.0323</v>
+        <v>0.267</v>
+      </c>
+      <c r="F3">
+        <v>-0.0539</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,10 +740,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="L3">
-        <v>0.04561620535023968</v>
+        <v>0.0951861583461405</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,55 +767,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2175.2</v>
+        <v>686.1</v>
       </c>
       <c r="V3">
-        <v>1.578634153421874</v>
+        <v>0.3387144549763034</v>
       </c>
       <c r="W3">
-        <v>0.0418766413514089</v>
+        <v>0.09165552797403093</v>
       </c>
       <c r="X3">
-        <v>0.1237364259668917</v>
+        <v>0.1738207871149478</v>
       </c>
       <c r="Y3">
-        <v>-0.08185978461548282</v>
+        <v>-0.08216525914091682</v>
       </c>
       <c r="Z3">
-        <v>56.57175348816855</v>
+        <v>4.8875696631936</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1185593084894753</v>
+        <v>0.1660909412797841</v>
       </c>
       <c r="AC3">
-        <v>-0.1185593084894753</v>
+        <v>-0.1660909412797841</v>
       </c>
       <c r="AD3">
-        <v>291.4</v>
+        <v>448.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>291.4</v>
+        <v>448.6</v>
       </c>
       <c r="AG3">
-        <v>-1883.8</v>
+        <v>-237.5</v>
       </c>
       <c r="AH3">
-        <v>0.1745641885820403</v>
+        <v>0.1813111308705845</v>
       </c>
       <c r="AI3">
-        <v>0.1457801790985042</v>
+        <v>0.1346015362457993</v>
       </c>
       <c r="AJ3">
-        <v>3.723660802530147</v>
+        <v>-0.1328225490744366</v>
       </c>
       <c r="AK3">
-        <v>10.68519568916621</v>
+        <v>-0.08973438621679829</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banco Macro S.A. (BASE:BMA)</t>
+          <t>Grupo Supervielle S.A. (BASE:SUPV)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.351</v>
-      </c>
-      <c r="E4">
-        <v>0.191</v>
+        <v>0.361</v>
       </c>
       <c r="F4">
-        <v>0.0556</v>
+        <v>-0.251</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>165</v>
+        <v>-20.1</v>
       </c>
       <c r="L4">
-        <v>0.1860622462787551</v>
+        <v>-0.05042649272453588</v>
       </c>
       <c r="M4">
-        <v>0.004</v>
+        <v>3.388</v>
       </c>
       <c r="N4">
-        <v>2.235261246158145e-06</v>
+        <v>0.00856853818917552</v>
       </c>
       <c r="O4">
-        <v>2.424242424242424e-05</v>
+        <v>-0.1685572139303483</v>
       </c>
       <c r="P4">
-        <v>0.004</v>
+        <v>0.538</v>
       </c>
       <c r="Q4">
-        <v>2.235261246158145e-06</v>
+        <v>0.001360647445624684</v>
       </c>
       <c r="R4">
-        <v>2.424242424242424e-05</v>
+        <v>-0.02676616915422885</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.8412042502951593</v>
       </c>
       <c r="U4">
-        <v>2162.2</v>
+        <v>145.1</v>
       </c>
       <c r="V4">
-        <v>1.208270466610785</v>
+        <v>0.3669701568032372</v>
       </c>
       <c r="W4">
-        <v>0.0938459788419975</v>
+        <v>-0.04059785901838012</v>
       </c>
       <c r="X4">
-        <v>0.1277312095471424</v>
+        <v>0.174234584140345</v>
       </c>
       <c r="Y4">
-        <v>-0.03388523070514493</v>
+        <v>-0.2148324431587251</v>
       </c>
       <c r="Z4">
-        <v>-12.778097982709</v>
+        <v>0.9454459203036053</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1213452191368887</v>
+        <v>0.1662747782336768</v>
       </c>
       <c r="AC4">
-        <v>-0.1213452191368887</v>
+        <v>-0.1662747782336768</v>
       </c>
       <c r="AD4">
-        <v>480.1</v>
+        <v>89.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>480.1</v>
+        <v>89.7</v>
       </c>
       <c r="AG4">
-        <v>-1682.1</v>
+        <v>-55.39999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.211535072259429</v>
+        <v>0.1849103277674707</v>
       </c>
       <c r="AI4">
-        <v>0.1864538428676842</v>
+        <v>0.14015625</v>
       </c>
       <c r="AJ4">
-        <v>-15.66201117318434</v>
+        <v>-0.1629411764705882</v>
       </c>
       <c r="AK4">
-        <v>-4.075842015992243</v>
+        <v>-0.1119418064255405</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.375</v>
+        <v>0.502</v>
       </c>
       <c r="E5">
-        <v>-0.0248</v>
+        <v>0.141</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,88 +975,91 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.005331499886892174</v>
+        <v>0.004912426130115719</v>
       </c>
       <c r="J5">
-        <v>0.00292037323239123</v>
+        <v>0.002663363564520571</v>
       </c>
       <c r="K5">
-        <v>28.2</v>
+        <v>45</v>
       </c>
       <c r="L5">
-        <v>0.06026928830946784</v>
+        <v>0.06901840490797546</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>20.1348</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.03975281342546891</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.4474400000000001</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>20.1348</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.03975281342546891</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.4474400000000001</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>174.5</v>
+        <v>210.7</v>
       </c>
       <c r="V5">
-        <v>0.2986479548177307</v>
+        <v>0.4159921026653504</v>
       </c>
       <c r="W5">
-        <v>0.04844528431540972</v>
+        <v>0.06787330316742081</v>
       </c>
       <c r="X5">
-        <v>0.1241105448156331</v>
+        <v>0.1744968498119949</v>
       </c>
       <c r="Y5">
-        <v>-0.07566526050022337</v>
+        <v>-0.1066235466445741</v>
       </c>
       <c r="Z5">
-        <v>1.01545876783204</v>
+        <v>1.060963947150459</v>
       </c>
       <c r="AA5">
-        <v>0.002965518604173671</v>
+        <v>0.002825732720110461</v>
       </c>
       <c r="AB5">
-        <v>0.1263437503573988</v>
+        <v>0.175941073016623</v>
       </c>
       <c r="AC5">
-        <v>-0.1233782317532251</v>
+        <v>-0.1731153402965125</v>
       </c>
       <c r="AD5">
-        <v>120.5</v>
+        <v>111.1</v>
       </c>
       <c r="AE5">
-        <v>6.17695601461576</v>
+        <v>5.535490815822754</v>
       </c>
       <c r="AF5">
-        <v>126.6769560146158</v>
+        <v>116.6354908158227</v>
       </c>
       <c r="AG5">
-        <v>-47.82304398538425</v>
+        <v>-94.06450918417724</v>
       </c>
       <c r="AH5">
-        <v>0.178173082746175</v>
+        <v>0.1871751690200168</v>
       </c>
       <c r="AI5">
-        <v>0.1604161740440494</v>
+        <v>0.1161898457296349</v>
       </c>
       <c r="AJ5">
-        <v>-0.08914277388660355</v>
+        <v>-0.228070840843769</v>
       </c>
       <c r="AK5">
-        <v>-0.0777386791195866</v>
+        <v>-0.1185982852531565</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1065,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>32.30563002680965</v>
+        <v>25.77726218097448</v>
       </c>
       <c r="AP5">
-        <v>-12.82119141699309</v>
+        <v>-21.82471210769774</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grupo Supervielle S.A. (BASE:SUPV)</t>
+          <t>Banco BBVA Argentina S.A. (BASE:BBAR)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,10 +1091,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.379</v>
-      </c>
-      <c r="F6">
-        <v>0.149</v>
+        <v>0.593</v>
+      </c>
+      <c r="E6">
+        <v>0.514</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1106,85 +1109,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-1.91</v>
+        <v>198.5</v>
       </c>
       <c r="L6">
-        <v>-0.004988247584225646</v>
+        <v>0.1338864157561042</v>
       </c>
       <c r="M6">
-        <v>2.89</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.007979017117614578</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-1.513089005235602</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>2.89</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.007979017117614578</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>-1.513089005235602</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>141.6</v>
+        <v>725.7</v>
       </c>
       <c r="V6">
-        <v>0.390944229707344</v>
+        <v>0.4608496856544104</v>
       </c>
       <c r="W6">
-        <v>-0.00457923759290338</v>
+        <v>0.1346949854108706</v>
       </c>
       <c r="X6">
-        <v>0.1318912654108914</v>
+        <v>0.1976088007641491</v>
       </c>
       <c r="Y6">
-        <v>-0.1364705030037948</v>
+        <v>-0.06291381535327845</v>
       </c>
       <c r="Z6">
-        <v>0.9129709108249878</v>
+        <v>0.9897856999799718</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1234183566309753</v>
+        <v>0.1745568344464097</v>
       </c>
       <c r="AC6">
-        <v>-0.1234183566309753</v>
+        <v>-0.1745568344464097</v>
       </c>
       <c r="AD6">
-        <v>118.6</v>
+        <v>837</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>118.6</v>
+        <v>837</v>
       </c>
       <c r="AG6">
-        <v>-23</v>
+        <v>111.3</v>
       </c>
       <c r="AH6">
-        <v>0.2466722129783694</v>
+        <v>0.347058091802463</v>
       </c>
       <c r="AI6">
-        <v>0.1931281550236118</v>
+        <v>0.2899504624657914</v>
       </c>
       <c r="AJ6">
-        <v>-0.06780660377358491</v>
+        <v>0.06601423487544482</v>
       </c>
       <c r="AK6">
-        <v>-0.04867724867724868</v>
+        <v>0.05150393336418323</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banco BBVA Argentina S.A. (BASE:BBAR)</t>
+          <t>Banco Hipotecario S.A. (BASE:BHIP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.471</v>
+        <v>0.405</v>
       </c>
       <c r="E7">
-        <v>0.238</v>
+        <v>0.448</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,85 +1228,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>125.3</v>
+        <v>51.9</v>
       </c>
       <c r="L7">
-        <v>0.1186328346903995</v>
+        <v>0.1457046603032005</v>
       </c>
       <c r="M7">
-        <v>136.6321</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.1021701188962836</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>1.090439744612929</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>136.6321</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.1021701188962836</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>1.090439744612929</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>529.4</v>
+        <v>138.1</v>
       </c>
       <c r="V7">
-        <v>0.3958722799670979</v>
+        <v>0.8846893017296604</v>
       </c>
       <c r="W7">
-        <v>0.09118032309707466</v>
+        <v>0.2605421686746988</v>
       </c>
       <c r="X7">
-        <v>0.1379759900973476</v>
+        <v>0.2106467968652581</v>
       </c>
       <c r="Y7">
-        <v>-0.04679566700027293</v>
+        <v>0.04989537180944068</v>
       </c>
       <c r="Z7">
-        <v>0.8377220812182741</v>
+        <v>0.9780340472267984</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1261382243276472</v>
+        <v>0.1778878863368962</v>
       </c>
       <c r="AC7">
-        <v>-0.1261382243276472</v>
+        <v>-0.1778878863368962</v>
       </c>
       <c r="AD7">
-        <v>553.6</v>
+        <v>109.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>553.6</v>
+        <v>109.5</v>
       </c>
       <c r="AG7">
-        <v>24.20000000000005</v>
+        <v>-28.59999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.2927706383203765</v>
+        <v>0.4122740963855421</v>
       </c>
       <c r="AI7">
-        <v>0.2691952346219305</v>
+        <v>0.2784842319430316</v>
       </c>
       <c r="AJ7">
-        <v>0.01777451340433349</v>
+        <v>-0.224313725490196</v>
       </c>
       <c r="AK7">
-        <v>0.01584703031890514</v>
+        <v>-0.1121128969031752</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1332,13 +1329,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.492</v>
+        <v>0.5770000000000001</v>
       </c>
       <c r="E8">
-        <v>0.259</v>
+        <v>0.19</v>
       </c>
       <c r="F8">
-        <v>0.227</v>
+        <v>-0.161</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>176.1</v>
+        <v>122.5</v>
       </c>
       <c r="L8">
-        <v>0.09590458555712884</v>
+        <v>0.0513347022587269</v>
       </c>
       <c r="M8">
-        <v>8.619999999999999</v>
+        <v>137</v>
       </c>
       <c r="N8">
-        <v>0.003074947383440944</v>
+        <v>0.04974040591075772</v>
       </c>
       <c r="O8">
-        <v>0.04894946053378762</v>
+        <v>1.118367346938776</v>
       </c>
       <c r="P8">
-        <v>8.619999999999999</v>
+        <v>137</v>
       </c>
       <c r="Q8">
-        <v>0.003074947383440944</v>
+        <v>0.04974040591075772</v>
       </c>
       <c r="R8">
-        <v>0.04894946053378762</v>
+        <v>1.118367346938776</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1383,179 +1380,60 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>2009.2</v>
+        <v>4253.3</v>
       </c>
       <c r="V8">
-        <v>0.7167267149431027</v>
+        <v>1.544239915768072</v>
       </c>
       <c r="W8">
-        <v>0.08657391475345362</v>
+        <v>0.04540400296515937</v>
       </c>
       <c r="X8">
-        <v>0.1537505569366308</v>
+        <v>0.2164246975860968</v>
       </c>
       <c r="Y8">
-        <v>-0.06717664218317722</v>
+        <v>-0.1710206946209374</v>
       </c>
       <c r="Z8">
-        <v>1.756792958285496</v>
+        <v>0.9629554900932165</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1318515799554767</v>
+        <v>0.1791603081568405</v>
       </c>
       <c r="AC8">
-        <v>-0.1318515799554767</v>
+        <v>-0.1791603081568405</v>
       </c>
       <c r="AD8">
-        <v>1789.3</v>
+        <v>2139.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1789.3</v>
+        <v>2139.5</v>
       </c>
       <c r="AG8">
-        <v>-219.9000000000001</v>
+        <v>-2113.8</v>
       </c>
       <c r="AH8">
-        <v>0.3896050167661019</v>
+        <v>0.4371858269647309</v>
       </c>
       <c r="AI8">
-        <v>0.3987475764936599</v>
+        <v>0.3865332152987299</v>
       </c>
       <c r="AJ8">
-        <v>-0.08512038399009061</v>
+        <v>-3.300234192037471</v>
       </c>
       <c r="AK8">
-        <v>-0.08873733909043223</v>
+        <v>-1.649087221095335</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Banco Hipotecario S.A. (BASE:BHIP)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.216</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>-38</v>
-      </c>
-      <c r="L9">
-        <v>-0.2149321266968326</v>
-      </c>
-      <c r="M9">
-        <v>0.058</v>
-      </c>
-      <c r="N9">
-        <v>0.0004625199362041468</v>
-      </c>
-      <c r="O9">
-        <v>-0.001526315789473684</v>
-      </c>
-      <c r="P9">
-        <v>0.058</v>
-      </c>
-      <c r="Q9">
-        <v>0.0004625199362041468</v>
-      </c>
-      <c r="R9">
-        <v>-0.001526315789473684</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>39.8</v>
-      </c>
-      <c r="V9">
-        <v>0.3173843700159489</v>
-      </c>
-      <c r="W9">
-        <v>-0.1912430800201309</v>
-      </c>
-      <c r="X9">
-        <v>0.2237145113927201</v>
-      </c>
-      <c r="Y9">
-        <v>-0.4149575914128509</v>
-      </c>
-      <c r="Z9">
-        <v>0.3463949843260188</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.1433106819104259</v>
-      </c>
-      <c r="AC9">
-        <v>-0.1433106819104259</v>
-      </c>
-      <c r="AD9">
-        <v>204.8</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>204.8</v>
-      </c>
-      <c r="AG9">
-        <v>165</v>
-      </c>
-      <c r="AH9">
-        <v>0.6202301635372501</v>
-      </c>
-      <c r="AI9">
-        <v>0.5001221001221001</v>
-      </c>
-      <c r="AJ9">
-        <v>0.5681818181818182</v>
-      </c>
-      <c r="AK9">
-        <v>0.4463078171490398</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/argentina/argentina_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.5395000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="E2">
-        <v>0.267</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="F2">
-        <v>-0.161</v>
+        <v>-0.0164</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0004391868468675198</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.0003379176766895401</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>589.8</v>
+        <v>798.3000000000001</v>
       </c>
       <c r="L2">
-        <v>0.0808742869679684</v>
+        <v>0.1179120570728033</v>
       </c>
       <c r="M2">
-        <v>160.5228</v>
+        <v>271.67</v>
       </c>
       <c r="N2">
-        <v>0.02165539756630602</v>
+        <v>0.04868201774034585</v>
       </c>
       <c r="O2">
-        <v>0.2721648016276704</v>
+        <v>0.3403106601528247</v>
       </c>
       <c r="P2">
-        <v>157.6728</v>
+        <v>268.98</v>
       </c>
       <c r="Q2">
-        <v>0.02127091708712192</v>
+        <v>0.04819998208045875</v>
       </c>
       <c r="R2">
-        <v>0.2673326551373347</v>
+        <v>0.3369409996242014</v>
       </c>
       <c r="S2">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="T2">
-        <v>0.01775448721303142</v>
+        <v>0.009901718997312915</v>
       </c>
       <c r="U2">
-        <v>6159</v>
+        <v>2380.1</v>
       </c>
       <c r="V2">
-        <v>0.8308825513315166</v>
+        <v>0.426503001523161</v>
       </c>
       <c r="W2">
-        <v>0.07976441557072586</v>
+        <v>0.1131114748136025</v>
       </c>
       <c r="X2">
-        <v>0.186052825288072</v>
+        <v>0.1453697386512247</v>
       </c>
       <c r="Y2">
-        <v>-0.1062884097173461</v>
+        <v>-0.03225826383762218</v>
       </c>
       <c r="Z2">
-        <v>1.259760803258136</v>
+        <v>1.477005977573193</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1752489537315164</v>
+        <v>0.1388463403248582</v>
       </c>
       <c r="AC2">
-        <v>-0.1738360873714611</v>
+        <v>-0.1388463403248582</v>
       </c>
       <c r="AD2">
-        <v>3735.4</v>
+        <v>2734.6</v>
       </c>
       <c r="AE2">
-        <v>5.535490815822754</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>3740.935490815823</v>
+        <v>2734.6</v>
       </c>
       <c r="AG2">
-        <v>-2418.064509184177</v>
+        <v>354.5</v>
       </c>
       <c r="AH2">
-        <v>0.3354035582615242</v>
+        <v>0.3288715709973422</v>
       </c>
       <c r="AI2">
-        <v>0.2712466910329091</v>
+        <v>0.2627755462879326</v>
       </c>
       <c r="AJ2">
-        <v>-0.4841420215414672</v>
+        <v>0.05973041280539174</v>
       </c>
       <c r="AK2">
-        <v>-0.3168059724709479</v>
+        <v>0.04416619946427459</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>866.6821345707658</v>
-      </c>
-      <c r="AP2">
-        <v>-561.035848998649</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banco Macro S.A. (BASE:BMA)</t>
+          <t>Grupo Supervielle S.A. (BASE:SUPV)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +713,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.581</v>
-      </c>
-      <c r="E3">
-        <v>0.267</v>
-      </c>
-      <c r="F3">
-        <v>-0.0539</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,19 +728,19 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>192</v>
+        <v>62.2</v>
       </c>
       <c r="L3">
-        <v>0.0951861583461405</v>
+        <v>0.1617264690587623</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.69</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.006260181521992088</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.04324758842443729</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -764,58 +752,61 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.69</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>686.1</v>
+        <v>185.2</v>
       </c>
       <c r="V3">
-        <v>0.3387144549763034</v>
+        <v>0.4309983709564812</v>
       </c>
       <c r="W3">
-        <v>0.09165552797403093</v>
+        <v>0.1131114748136025</v>
       </c>
       <c r="X3">
-        <v>0.1738207871149478</v>
+        <v>0.1360288137366876</v>
       </c>
       <c r="Y3">
-        <v>-0.08216525914091682</v>
+        <v>-0.02291733892308515</v>
       </c>
       <c r="Z3">
-        <v>4.8875696631936</v>
+        <v>0.8890429958391124</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1660909412797841</v>
+        <v>0.1333211979400548</v>
       </c>
       <c r="AC3">
-        <v>-0.1660909412797841</v>
+        <v>-0.1333211979400548</v>
       </c>
       <c r="AD3">
-        <v>448.6</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>448.6</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>-237.5</v>
+        <v>-109.1</v>
       </c>
       <c r="AH3">
-        <v>0.1813111308705845</v>
+        <v>0.1504547251878213</v>
       </c>
       <c r="AI3">
-        <v>0.1346015362457993</v>
+        <v>0.1140929535232384</v>
       </c>
       <c r="AJ3">
-        <v>-0.1328225490744366</v>
+        <v>-0.3402994385527136</v>
       </c>
       <c r="AK3">
-        <v>-0.08973438621679829</v>
+        <v>-0.2264425072644251</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grupo Supervielle S.A. (BASE:SUPV)</t>
+          <t>Banco Patagonia S.A. (BASE:BPAT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.361</v>
-      </c>
-      <c r="F4">
-        <v>-0.251</v>
+        <v>0.903</v>
+      </c>
+      <c r="E4">
+        <v>0.605</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +850,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-20.1</v>
+        <v>122.8</v>
       </c>
       <c r="L4">
-        <v>-0.05042649272453588</v>
+        <v>0.1083465678489501</v>
       </c>
       <c r="M4">
-        <v>3.388</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.00856853818917552</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.1685572139303483</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.538</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.001360647445624684</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0.02676616915422885</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>2.85</v>
-      </c>
-      <c r="T4">
-        <v>0.8412042502951593</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>145.1</v>
+        <v>216.5</v>
       </c>
       <c r="V4">
-        <v>0.3669701568032372</v>
+        <v>0.4036167039522744</v>
       </c>
       <c r="W4">
-        <v>-0.04059785901838012</v>
+        <v>0.1384129846708747</v>
       </c>
       <c r="X4">
-        <v>0.174234584140345</v>
+        <v>0.1332926465702797</v>
       </c>
       <c r="Y4">
-        <v>-0.2148324431587251</v>
+        <v>0.005120338100594951</v>
       </c>
       <c r="Z4">
-        <v>0.9454459203036053</v>
+        <v>1.439055358049771</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1662747782336768</v>
+        <v>0.1381821877614215</v>
       </c>
       <c r="AC4">
-        <v>-0.1662747782336768</v>
+        <v>-0.1381821877614215</v>
       </c>
       <c r="AD4">
-        <v>89.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>89.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AG4">
-        <v>-55.39999999999999</v>
+        <v>-147.4</v>
       </c>
       <c r="AH4">
-        <v>0.1849103277674707</v>
+        <v>0.1141205615194054</v>
       </c>
       <c r="AI4">
-        <v>0.14015625</v>
+        <v>0.06677618863548511</v>
       </c>
       <c r="AJ4">
-        <v>-0.1629411764705882</v>
+        <v>-0.3789203084832905</v>
       </c>
       <c r="AK4">
-        <v>-0.1119418064255405</v>
+        <v>-0.180129536844678</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banco Patagonia S.A. (BASE:BPAT)</t>
+          <t>Banco Hipotecario S.A. (BASE:BHIP)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +951,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.502</v>
+        <v>0.522</v>
       </c>
       <c r="E5">
-        <v>0.141</v>
+        <v>0.442</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,103 +963,94 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.004912426130115719</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.002663363564520571</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>45</v>
+        <v>28.7</v>
       </c>
       <c r="L5">
-        <v>0.06901840490797546</v>
+        <v>0.09376020908199934</v>
       </c>
       <c r="M5">
-        <v>20.1348</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.03975281342546891</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4474400000000001</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>20.1348</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03975281342546891</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4474400000000001</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>210.7</v>
+        <v>117.3</v>
       </c>
       <c r="V5">
-        <v>0.4159921026653504</v>
+        <v>0.5593705293276109</v>
       </c>
       <c r="W5">
-        <v>0.06787330316742081</v>
+        <v>0.1034607065609229</v>
       </c>
       <c r="X5">
-        <v>0.1744968498119949</v>
+        <v>0.1453697386512247</v>
       </c>
       <c r="Y5">
-        <v>-0.1066235466445741</v>
+        <v>-0.04190903209030179</v>
       </c>
       <c r="Z5">
-        <v>1.060963947150459</v>
+        <v>1.230305466237942</v>
       </c>
       <c r="AA5">
-        <v>0.002825732720110461</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.175941073016623</v>
+        <v>0.1388463403248582</v>
       </c>
       <c r="AC5">
-        <v>-0.1731153402965125</v>
+        <v>-0.1388463403248582</v>
       </c>
       <c r="AD5">
-        <v>111.1</v>
+        <v>71.7</v>
       </c>
       <c r="AE5">
-        <v>5.535490815822754</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>116.6354908158227</v>
+        <v>71.7</v>
       </c>
       <c r="AG5">
-        <v>-94.06450918417724</v>
+        <v>-45.59999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.1871751690200168</v>
+        <v>0.2547974413646056</v>
       </c>
       <c r="AI5">
-        <v>0.1161898457296349</v>
+        <v>0.1766009852216749</v>
       </c>
       <c r="AJ5">
-        <v>-0.228070840843769</v>
+        <v>-0.2778793418647166</v>
       </c>
       <c r="AK5">
-        <v>-0.1185982852531565</v>
+        <v>-0.1579494284724627</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>25.77726218097448</v>
-      </c>
-      <c r="AP5">
-        <v>-21.82471210769774</v>
       </c>
     </row>
     <row r="6">
@@ -1091,10 +1070,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.593</v>
+        <v>0.733</v>
       </c>
       <c r="E6">
-        <v>0.514</v>
+        <v>0.555</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,82 +1088,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>198.5</v>
+        <v>142.3</v>
       </c>
       <c r="L6">
-        <v>0.1338864157561042</v>
+        <v>0.07735797771133461</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>7.68</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.005707915273132664</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.05397048489107518</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>7.68</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.005707915273132664</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.05397048489107518</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>725.7</v>
+        <v>773.3</v>
       </c>
       <c r="V6">
-        <v>0.4608496856544104</v>
+        <v>0.5747305834262356</v>
       </c>
       <c r="W6">
-        <v>0.1346949854108706</v>
+        <v>0.07054682464924893</v>
       </c>
       <c r="X6">
-        <v>0.1976088007641491</v>
+        <v>0.1488174191062621</v>
       </c>
       <c r="Y6">
-        <v>-0.06291381535327845</v>
+        <v>-0.07827059445701313</v>
       </c>
       <c r="Z6">
-        <v>0.9897856999799718</v>
+        <v>1.00354609929078</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1745568344464097</v>
+        <v>0.1399786488771427</v>
       </c>
       <c r="AC6">
-        <v>-0.1745568344464097</v>
+        <v>-0.1399786488771427</v>
       </c>
       <c r="AD6">
-        <v>837</v>
+        <v>541.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>837</v>
+        <v>541.9</v>
       </c>
       <c r="AG6">
-        <v>111.3</v>
+        <v>-231.4</v>
       </c>
       <c r="AH6">
-        <v>0.347058091802463</v>
+        <v>0.2871145491151849</v>
       </c>
       <c r="AI6">
-        <v>0.2899504624657914</v>
+        <v>0.1987675604298866</v>
       </c>
       <c r="AJ6">
-        <v>0.06601423487544482</v>
+        <v>-0.2077012835472579</v>
       </c>
       <c r="AK6">
-        <v>0.05150393336418323</v>
+        <v>-0.118484383000512</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,7 +1183,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banco Hipotecario S.A. (BASE:BHIP)</t>
+          <t>Grupo Financiero Galicia S.A. (BASE:GGAL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,10 +1192,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.405</v>
+        <v>0.675</v>
       </c>
       <c r="E7">
-        <v>0.448</v>
+        <v>0.6970000000000001</v>
+      </c>
+      <c r="F7">
+        <v>-0.0164</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,212 +1213,90 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>51.9</v>
+        <v>442.3</v>
       </c>
       <c r="L7">
-        <v>0.1457046603032005</v>
+        <v>0.1423697170631217</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>261.3</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.08541448744769875</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.5907754917476826</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>261.3</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.08541448744769875</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.5907754917476826</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>138.1</v>
+        <v>1087.8</v>
       </c>
       <c r="V7">
-        <v>0.8846893017296604</v>
+        <v>0.3555831589958159</v>
       </c>
       <c r="W7">
-        <v>0.2605421686746988</v>
+        <v>0.1302568029214277</v>
       </c>
       <c r="X7">
-        <v>0.2106467968652581</v>
+        <v>0.1625953147412776</v>
       </c>
       <c r="Y7">
-        <v>0.04989537180944068</v>
+        <v>-0.0323385118198499</v>
       </c>
       <c r="Z7">
-        <v>0.9780340472267984</v>
+        <v>2.423701045404899</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1778878863368962</v>
+        <v>0.1451083202830376</v>
       </c>
       <c r="AC7">
-        <v>-0.1778878863368962</v>
+        <v>-0.1451083202830376</v>
       </c>
       <c r="AD7">
-        <v>109.5</v>
+        <v>1975.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>109.5</v>
+        <v>1975.8</v>
       </c>
       <c r="AG7">
-        <v>-28.59999999999999</v>
+        <v>888</v>
       </c>
       <c r="AH7">
-        <v>0.4122740963855421</v>
+        <v>0.3924131082423039</v>
       </c>
       <c r="AI7">
-        <v>0.2784842319430316</v>
+        <v>0.3545625841184388</v>
       </c>
       <c r="AJ7">
-        <v>-0.224313725490196</v>
+        <v>0.224969598702878</v>
       </c>
       <c r="AK7">
-        <v>-0.1121128969031752</v>
+        <v>0.1980065556224497</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Grupo Financiero Galicia S.A. (BASE:GGAL)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.5770000000000001</v>
-      </c>
-      <c r="E8">
-        <v>0.19</v>
-      </c>
-      <c r="F8">
-        <v>-0.161</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>122.5</v>
-      </c>
-      <c r="L8">
-        <v>0.0513347022587269</v>
-      </c>
-      <c r="M8">
-        <v>137</v>
-      </c>
-      <c r="N8">
-        <v>0.04974040591075772</v>
-      </c>
-      <c r="O8">
-        <v>1.118367346938776</v>
-      </c>
-      <c r="P8">
-        <v>137</v>
-      </c>
-      <c r="Q8">
-        <v>0.04974040591075772</v>
-      </c>
-      <c r="R8">
-        <v>1.118367346938776</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>4253.3</v>
-      </c>
-      <c r="V8">
-        <v>1.544239915768072</v>
-      </c>
-      <c r="W8">
-        <v>0.04540400296515937</v>
-      </c>
-      <c r="X8">
-        <v>0.2164246975860968</v>
-      </c>
-      <c r="Y8">
-        <v>-0.1710206946209374</v>
-      </c>
-      <c r="Z8">
-        <v>0.9629554900932165</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.1791603081568405</v>
-      </c>
-      <c r="AC8">
-        <v>-0.1791603081568405</v>
-      </c>
-      <c r="AD8">
-        <v>2139.5</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>2139.5</v>
-      </c>
-      <c r="AG8">
-        <v>-2113.8</v>
-      </c>
-      <c r="AH8">
-        <v>0.4371858269647309</v>
-      </c>
-      <c r="AI8">
-        <v>0.3865332152987299</v>
-      </c>
-      <c r="AJ8">
-        <v>-3.300234192037471</v>
-      </c>
-      <c r="AK8">
-        <v>-1.649087221095335</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/argentina/argentina_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.675</v>
+        <v>0.8059999999999999</v>
       </c>
       <c r="E2">
-        <v>0.5800000000000001</v>
-      </c>
-      <c r="F2">
-        <v>-0.0164</v>
+        <v>0.547</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>798.3000000000001</v>
+        <v>127.7</v>
       </c>
       <c r="L2">
-        <v>0.1179120570728033</v>
+        <v>0.1287168632194335</v>
       </c>
       <c r="M2">
-        <v>271.67</v>
+        <v>5.69</v>
       </c>
       <c r="N2">
-        <v>0.04868201774034585</v>
+        <v>0.003032240873967493</v>
       </c>
       <c r="O2">
-        <v>0.3403106601528247</v>
+        <v>0.04455755677368833</v>
       </c>
       <c r="P2">
-        <v>268.98</v>
+        <v>5.69</v>
       </c>
       <c r="Q2">
-        <v>0.04819998208045875</v>
+        <v>0.003032240873967493</v>
       </c>
       <c r="R2">
-        <v>0.3369409996242014</v>
+        <v>0.04455755677368833</v>
       </c>
       <c r="S2">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.009901718997312915</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2380.1</v>
+        <v>490.2</v>
       </c>
       <c r="V2">
-        <v>0.426503001523161</v>
+        <v>0.2612310151878497</v>
       </c>
       <c r="W2">
-        <v>0.1131114748136025</v>
+        <v>0.1345910623946037</v>
       </c>
       <c r="X2">
-        <v>0.1453697386512247</v>
+        <v>0.126800579980315</v>
       </c>
       <c r="Y2">
-        <v>-0.03225826383762218</v>
+        <v>0.007790482414288757</v>
       </c>
       <c r="Z2">
-        <v>1.477005977573193</v>
+        <v>1.12995444191344</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1388463403248582</v>
+        <v>0.1272708747999917</v>
       </c>
       <c r="AC2">
-        <v>-0.1388463403248582</v>
+        <v>-0.1272708747999917</v>
       </c>
       <c r="AD2">
-        <v>2734.6</v>
+        <v>32.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2734.6</v>
+        <v>32.6</v>
       </c>
       <c r="AG2">
-        <v>354.5</v>
+        <v>-457.6</v>
       </c>
       <c r="AH2">
-        <v>0.3288715709973422</v>
+        <v>0.01707610916138495</v>
       </c>
       <c r="AI2">
-        <v>0.2627755462879326</v>
+        <v>0.02574836110891715</v>
       </c>
       <c r="AJ2">
-        <v>0.05973041280539174</v>
+        <v>-0.3225033476636831</v>
       </c>
       <c r="AK2">
-        <v>0.04416619946427459</v>
+        <v>-0.589766722515788</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grupo Supervielle S.A. (BASE:SUPV)</t>
+          <t>Banco Patagonia S.A. (BASE:BPAT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,7 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.4320000000000001</v>
+        <v>0.8059999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.547</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,575 +728,90 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>62.2</v>
+        <v>127.7</v>
       </c>
       <c r="L3">
-        <v>0.1617264690587623</v>
+        <v>0.1287168632194335</v>
       </c>
       <c r="M3">
-        <v>2.69</v>
+        <v>5.69</v>
       </c>
       <c r="N3">
-        <v>0.006260181521992088</v>
+        <v>0.003032240873967493</v>
       </c>
       <c r="O3">
-        <v>0.04324758842443729</v>
+        <v>0.04455755677368833</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>5.69</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.003032240873967493</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.04455755677368833</v>
       </c>
       <c r="S3">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>185.2</v>
+        <v>490.2</v>
       </c>
       <c r="V3">
-        <v>0.4309983709564812</v>
+        <v>0.2612310151878497</v>
       </c>
       <c r="W3">
-        <v>0.1131114748136025</v>
+        <v>0.1345910623946037</v>
       </c>
       <c r="X3">
-        <v>0.1360288137366876</v>
+        <v>0.126800579980315</v>
       </c>
       <c r="Y3">
-        <v>-0.02291733892308515</v>
+        <v>0.007790482414288757</v>
       </c>
       <c r="Z3">
-        <v>0.8890429958391124</v>
+        <v>1.12995444191344</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1333211979400548</v>
+        <v>0.1272708747999917</v>
       </c>
       <c r="AC3">
-        <v>-0.1333211979400548</v>
+        <v>-0.1272708747999917</v>
       </c>
       <c r="AD3">
-        <v>76.09999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>76.09999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="AG3">
-        <v>-109.1</v>
+        <v>-457.6</v>
       </c>
       <c r="AH3">
-        <v>0.1504547251878213</v>
+        <v>0.01707610916138495</v>
       </c>
       <c r="AI3">
-        <v>0.1140929535232384</v>
+        <v>0.02574836110891715</v>
       </c>
       <c r="AJ3">
-        <v>-0.3402994385527136</v>
+        <v>-0.3225033476636831</v>
       </c>
       <c r="AK3">
-        <v>-0.2264425072644251</v>
+        <v>-0.589766722515788</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Banco Patagonia S.A. (BASE:BPAT)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.903</v>
-      </c>
-      <c r="E4">
-        <v>0.605</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>122.8</v>
-      </c>
-      <c r="L4">
-        <v>0.1083465678489501</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>216.5</v>
-      </c>
-      <c r="V4">
-        <v>0.4036167039522744</v>
-      </c>
-      <c r="W4">
-        <v>0.1384129846708747</v>
-      </c>
-      <c r="X4">
-        <v>0.1332926465702797</v>
-      </c>
-      <c r="Y4">
-        <v>0.005120338100594951</v>
-      </c>
-      <c r="Z4">
-        <v>1.439055358049771</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.1381821877614215</v>
-      </c>
-      <c r="AC4">
-        <v>-0.1381821877614215</v>
-      </c>
-      <c r="AD4">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="AG4">
-        <v>-147.4</v>
-      </c>
-      <c r="AH4">
-        <v>0.1141205615194054</v>
-      </c>
-      <c r="AI4">
-        <v>0.06677618863548511</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.3789203084832905</v>
-      </c>
-      <c r="AK4">
-        <v>-0.180129536844678</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Banco Hipotecario S.A. (BASE:BHIP)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.522</v>
-      </c>
-      <c r="E5">
-        <v>0.442</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>28.7</v>
-      </c>
-      <c r="L5">
-        <v>0.09376020908199934</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>117.3</v>
-      </c>
-      <c r="V5">
-        <v>0.5593705293276109</v>
-      </c>
-      <c r="W5">
-        <v>0.1034607065609229</v>
-      </c>
-      <c r="X5">
-        <v>0.1453697386512247</v>
-      </c>
-      <c r="Y5">
-        <v>-0.04190903209030179</v>
-      </c>
-      <c r="Z5">
-        <v>1.230305466237942</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.1388463403248582</v>
-      </c>
-      <c r="AC5">
-        <v>-0.1388463403248582</v>
-      </c>
-      <c r="AD5">
-        <v>71.7</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>71.7</v>
-      </c>
-      <c r="AG5">
-        <v>-45.59999999999999</v>
-      </c>
-      <c r="AH5">
-        <v>0.2547974413646056</v>
-      </c>
-      <c r="AI5">
-        <v>0.1766009852216749</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.2778793418647166</v>
-      </c>
-      <c r="AK5">
-        <v>-0.1579494284724627</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Banco BBVA Argentina S.A. (BASE:BBAR)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.733</v>
-      </c>
-      <c r="E6">
-        <v>0.555</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>142.3</v>
-      </c>
-      <c r="L6">
-        <v>0.07735797771133461</v>
-      </c>
-      <c r="M6">
-        <v>7.68</v>
-      </c>
-      <c r="N6">
-        <v>0.005707915273132664</v>
-      </c>
-      <c r="O6">
-        <v>0.05397048489107518</v>
-      </c>
-      <c r="P6">
-        <v>7.68</v>
-      </c>
-      <c r="Q6">
-        <v>0.005707915273132664</v>
-      </c>
-      <c r="R6">
-        <v>0.05397048489107518</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>773.3</v>
-      </c>
-      <c r="V6">
-        <v>0.5747305834262356</v>
-      </c>
-      <c r="W6">
-        <v>0.07054682464924893</v>
-      </c>
-      <c r="X6">
-        <v>0.1488174191062621</v>
-      </c>
-      <c r="Y6">
-        <v>-0.07827059445701313</v>
-      </c>
-      <c r="Z6">
-        <v>1.00354609929078</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.1399786488771427</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1399786488771427</v>
-      </c>
-      <c r="AD6">
-        <v>541.9</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>541.9</v>
-      </c>
-      <c r="AG6">
-        <v>-231.4</v>
-      </c>
-      <c r="AH6">
-        <v>0.2871145491151849</v>
-      </c>
-      <c r="AI6">
-        <v>0.1987675604298866</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.2077012835472579</v>
-      </c>
-      <c r="AK6">
-        <v>-0.118484383000512</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Grupo Financiero Galicia S.A. (BASE:GGAL)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.675</v>
-      </c>
-      <c r="E7">
-        <v>0.6970000000000001</v>
-      </c>
-      <c r="F7">
-        <v>-0.0164</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>442.3</v>
-      </c>
-      <c r="L7">
-        <v>0.1423697170631217</v>
-      </c>
-      <c r="M7">
-        <v>261.3</v>
-      </c>
-      <c r="N7">
-        <v>0.08541448744769875</v>
-      </c>
-      <c r="O7">
-        <v>0.5907754917476826</v>
-      </c>
-      <c r="P7">
-        <v>261.3</v>
-      </c>
-      <c r="Q7">
-        <v>0.08541448744769875</v>
-      </c>
-      <c r="R7">
-        <v>0.5907754917476826</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>1087.8</v>
-      </c>
-      <c r="V7">
-        <v>0.3555831589958159</v>
-      </c>
-      <c r="W7">
-        <v>0.1302568029214277</v>
-      </c>
-      <c r="X7">
-        <v>0.1625953147412776</v>
-      </c>
-      <c r="Y7">
-        <v>-0.0323385118198499</v>
-      </c>
-      <c r="Z7">
-        <v>2.423701045404899</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.1451083202830376</v>
-      </c>
-      <c r="AC7">
-        <v>-0.1451083202830376</v>
-      </c>
-      <c r="AD7">
-        <v>1975.8</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>1975.8</v>
-      </c>
-      <c r="AG7">
-        <v>888</v>
-      </c>
-      <c r="AH7">
-        <v>0.3924131082423039</v>
-      </c>
-      <c r="AI7">
-        <v>0.3545625841184388</v>
-      </c>
-      <c r="AJ7">
-        <v>0.224969598702878</v>
-      </c>
-      <c r="AK7">
-        <v>0.1980065556224497</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/argentina/argentina_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.8059999999999999</v>
+        <v>0.8205</v>
       </c>
       <c r="E2">
-        <v>0.547</v>
+        <v>0.8105</v>
+      </c>
+      <c r="F2">
+        <v>0.12385</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>127.7</v>
+        <v>1879.2</v>
       </c>
       <c r="L2">
-        <v>0.1287168632194335</v>
+        <v>0.1661024439828523</v>
       </c>
       <c r="M2">
-        <v>5.69</v>
+        <v>899.8912</v>
       </c>
       <c r="N2">
-        <v>0.003032240873967493</v>
+        <v>0.03397456884834939</v>
       </c>
       <c r="O2">
-        <v>0.04455755677368833</v>
+        <v>0.478869306087697</v>
       </c>
       <c r="P2">
-        <v>5.69</v>
+        <v>891.3212</v>
       </c>
       <c r="Q2">
-        <v>0.003032240873967493</v>
+        <v>0.03365101633996798</v>
       </c>
       <c r="R2">
-        <v>0.04455755677368833</v>
+        <v>0.4743088548318434</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>8.569999999999997</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.009523373492262172</v>
       </c>
       <c r="U2">
-        <v>490.2</v>
+        <v>7260.8</v>
       </c>
       <c r="V2">
-        <v>0.2612310151878497</v>
+        <v>0.2741248603098855</v>
       </c>
       <c r="W2">
-        <v>0.1345910623946037</v>
+        <v>0.170094877639806</v>
       </c>
       <c r="X2">
-        <v>0.126800579980315</v>
+        <v>0.1284275771969267</v>
       </c>
       <c r="Y2">
-        <v>0.007790482414288757</v>
+        <v>0.04166730044287931</v>
       </c>
       <c r="Z2">
-        <v>1.12995444191344</v>
+        <v>1.172541378631318</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1272708747999917</v>
+        <v>0.1278880494281531</v>
       </c>
       <c r="AC2">
-        <v>-0.1272708747999917</v>
+        <v>-0.1278880494281531</v>
       </c>
       <c r="AD2">
-        <v>32.6</v>
+        <v>3971.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>32.6</v>
+        <v>3971.9</v>
       </c>
       <c r="AG2">
-        <v>-457.6</v>
+        <v>-3288.9</v>
       </c>
       <c r="AH2">
-        <v>0.01707610916138495</v>
+        <v>0.1304010952391896</v>
       </c>
       <c r="AI2">
-        <v>0.02574836110891715</v>
+        <v>0.286149634379165</v>
       </c>
       <c r="AJ2">
-        <v>-0.3225033476636831</v>
+        <v>-0.1417733195966946</v>
       </c>
       <c r="AK2">
-        <v>-0.589766722515788</v>
+        <v>-0.4968352040122664</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,117 +704,724 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Banco Macro S.A. (BASE:BMA)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>1.036</v>
+      </c>
+      <c r="E3">
+        <v>0.903</v>
+      </c>
+      <c r="F3">
+        <v>-0.0303</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>568.3</v>
+      </c>
+      <c r="L3">
+        <v>0.2023283964682426</v>
+      </c>
+      <c r="M3">
+        <v>414.3312</v>
+      </c>
+      <c r="N3">
+        <v>0.05851804982769335</v>
+      </c>
+      <c r="O3">
+        <v>0.7290712651768433</v>
+      </c>
+      <c r="P3">
+        <v>414.3312</v>
+      </c>
+      <c r="Q3">
+        <v>0.05851804982769335</v>
+      </c>
+      <c r="R3">
+        <v>0.7290712651768433</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>53.5</v>
+      </c>
+      <c r="V3">
+        <v>0.007556070278515338</v>
+      </c>
+      <c r="W3">
+        <v>0.1974292166058711</v>
+      </c>
+      <c r="X3">
+        <v>0.126190836717647</v>
+      </c>
+      <c r="Y3">
+        <v>0.07123837988822407</v>
+      </c>
+      <c r="Z3">
+        <v>1.798898424490841</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.1261310982472433</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1261310982472433</v>
+      </c>
+      <c r="AD3">
+        <v>37.4</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>37.4</v>
+      </c>
+      <c r="AG3">
+        <v>-16.1</v>
+      </c>
+      <c r="AH3">
+        <v>0.005254432549383237</v>
+      </c>
+      <c r="AI3">
+        <v>0.08256070640176601</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.002279065158614442</v>
+      </c>
+      <c r="AK3">
+        <v>-0.04030037546933667</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Banco Patagonia S.A. (BASE:BPAT)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>0.8059999999999999</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>0.547</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>127.7</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>0.1287168632194335</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>5.69</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>0.003032240873967493</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>0.04455755677368833</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>5.69</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>0.003032240873967493</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>0.04455755677368833</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>490.2</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>0.2612310151878497</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>0.1345910623946037</v>
       </c>
-      <c r="X3">
-        <v>0.126800579980315</v>
-      </c>
-      <c r="Y3">
-        <v>0.007790482414288757</v>
-      </c>
-      <c r="Z3">
+      <c r="X4">
+        <v>0.1268204567167902</v>
+      </c>
+      <c r="Y4">
+        <v>0.007770605677813541</v>
+      </c>
+      <c r="Z4">
         <v>1.12995444191344</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.1272708747999917</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1272708747999917</v>
-      </c>
-      <c r="AD3">
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.1272904121191451</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1272904121191451</v>
+      </c>
+      <c r="AD4">
         <v>32.6</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>32.6</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>-457.6</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.01707610916138495</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.02574836110891715</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>-0.3225033476636831</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>-0.589766722515788</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Banco Hipotecario S.A. (BASE:BHIP)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.835</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>63.3</v>
+      </c>
+      <c r="L5">
+        <v>0.1387853540890155</v>
+      </c>
+      <c r="M5">
+        <v>46.9</v>
+      </c>
+      <c r="N5">
+        <v>0.05438311688311688</v>
+      </c>
+      <c r="O5">
+        <v>0.740916271721959</v>
+      </c>
+      <c r="P5">
+        <v>46.9</v>
+      </c>
+      <c r="Q5">
+        <v>0.05438311688311688</v>
+      </c>
+      <c r="R5">
+        <v>0.740916271721959</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="V5">
+        <v>0.100417439703154</v>
+      </c>
+      <c r="W5">
+        <v>0.1948891625615763</v>
+      </c>
+      <c r="X5">
+        <v>0.1282284765168007</v>
+      </c>
+      <c r="Y5">
+        <v>0.0666606860447756</v>
+      </c>
+      <c r="Z5">
+        <v>1.196798740488061</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.1278325157856398</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1278325157856398</v>
+      </c>
+      <c r="AD5">
+        <v>38.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>38.3</v>
+      </c>
+      <c r="AG5">
+        <v>-48.3</v>
+      </c>
+      <c r="AH5">
+        <v>0.04252248251360053</v>
+      </c>
+      <c r="AI5">
+        <v>0.0793782383419689</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.05932932072226998</v>
+      </c>
+      <c r="AK5">
+        <v>-0.1220005051780753</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Banco BBVA Argentina S.A. (BASE:BBAR)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.754</v>
+      </c>
+      <c r="E6">
+        <v>0.718</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>208.8</v>
+      </c>
+      <c r="L6">
+        <v>0.09551692589204026</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>2070.2</v>
+      </c>
+      <c r="V6">
+        <v>0.4607509292025549</v>
+      </c>
+      <c r="W6">
+        <v>0.09705759308325199</v>
+      </c>
+      <c r="X6">
+        <v>0.1286266778770525</v>
+      </c>
+      <c r="Y6">
+        <v>-0.03156908479380055</v>
+      </c>
+      <c r="Z6">
+        <v>1.138600968800458</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.1279435830706664</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1279435830706664</v>
+      </c>
+      <c r="AD6">
+        <v>233.9</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>233.9</v>
+      </c>
+      <c r="AG6">
+        <v>-1836.3</v>
+      </c>
+      <c r="AH6">
+        <v>0.04948170086735773</v>
+      </c>
+      <c r="AI6">
+        <v>0.08667136028458146</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.69116982836495</v>
+      </c>
+      <c r="AK6">
+        <v>-2.921718377088303</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grupo Supervielle S.A. (BASE:SUPV)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.637</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>85.8</v>
+      </c>
+      <c r="L7">
+        <v>0.1969244893275189</v>
+      </c>
+      <c r="M7">
+        <v>35.27</v>
+      </c>
+      <c r="N7">
+        <v>0.02323604980565254</v>
+      </c>
+      <c r="O7">
+        <v>0.411072261072261</v>
+      </c>
+      <c r="P7">
+        <v>26.7</v>
+      </c>
+      <c r="Q7">
+        <v>0.01759009157388497</v>
+      </c>
+      <c r="R7">
+        <v>0.3111888111888112</v>
+      </c>
+      <c r="S7">
+        <v>8.569999999999997</v>
+      </c>
+      <c r="T7">
+        <v>0.2429827048483129</v>
+      </c>
+      <c r="U7">
+        <v>389.5</v>
+      </c>
+      <c r="V7">
+        <v>0.2566045194018051</v>
+      </c>
+      <c r="W7">
+        <v>0.1453005927180356</v>
+      </c>
+      <c r="X7">
+        <v>0.132739513270194</v>
+      </c>
+      <c r="Y7">
+        <v>0.01256107944784152</v>
+      </c>
+      <c r="Z7">
+        <v>1.028564683663834</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.1306636412047888</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1306636412047888</v>
+      </c>
+      <c r="AD7">
+        <v>198.9</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>198.9</v>
+      </c>
+      <c r="AG7">
+        <v>-190.6</v>
+      </c>
+      <c r="AH7">
+        <v>0.1158550792171482</v>
+      </c>
+      <c r="AI7">
+        <v>0.2072522663332292</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.1435997890454306</v>
+      </c>
+      <c r="AK7">
+        <v>-0.3342686776569625</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grupo Financiero Galicia S.A. (BASE:GGAL)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.835</v>
+      </c>
+      <c r="E8">
+        <v>1.392</v>
+      </c>
+      <c r="F8">
+        <v>0.278</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>825.3</v>
+      </c>
+      <c r="L8">
+        <v>0.1860963290340038</v>
+      </c>
+      <c r="M8">
+        <v>397.7</v>
+      </c>
+      <c r="N8">
+        <v>0.0373185447925757</v>
+      </c>
+      <c r="O8">
+        <v>0.481885375015146</v>
+      </c>
+      <c r="P8">
+        <v>397.7</v>
+      </c>
+      <c r="Q8">
+        <v>0.0373185447925757</v>
+      </c>
+      <c r="R8">
+        <v>0.481885375015146</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>4170.8</v>
+      </c>
+      <c r="V8">
+        <v>0.3913708489335548</v>
+      </c>
+      <c r="W8">
+        <v>0.2294603386437568</v>
+      </c>
+      <c r="X8">
+        <v>0.1426804681210619</v>
+      </c>
+      <c r="Y8">
+        <v>0.08677987052269492</v>
+      </c>
+      <c r="Z8">
+        <v>0.9888732802640088</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.1355002341274154</v>
+      </c>
+      <c r="AC8">
+        <v>-0.1355002341274154</v>
+      </c>
+      <c r="AD8">
+        <v>3430.8</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>3430.8</v>
+      </c>
+      <c r="AG8">
+        <v>-740</v>
+      </c>
+      <c r="AH8">
+        <v>0.2435315913882323</v>
+      </c>
+      <c r="AI8">
+        <v>0.4277538806807556</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.07462009297260233</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1922227706055017</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>
